--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-26T10:57:55.240Z</t>
+    <t>2026-06-26T12:15:02.734Z</t>
   </si>
   <si>
     <t>Semrush: Your Unfair Advantage for Growing Brand Visibility</t>
